--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/product_desc_length.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/product_desc_length.xlsx
@@ -455,7 +455,7 @@
         <v>70</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>30.36</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>23.66</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
-        <v>14.5</v>
+        <v>14.73</v>
       </c>
     </row>
   </sheetData>
